--- a/app1/Excelfiles/test.xlsx
+++ b/app1/Excelfiles/test.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -523,7 +523,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ew</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ew</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,13 +646,58 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="F23" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="F24" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="F25" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="F29" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
